--- a/data/trans_orig/P36BPD07_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_R-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>370373</t>
+          <t>370697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>395608</t>
+          <t>395131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>295008</t>
+          <t>297440</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>318307</t>
+          <t>319475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>675339</t>
+          <t>675551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>708019</t>
+          <t>708594</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29347</t>
+          <t>29824</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54582</t>
+          <t>54258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27504</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50803</t>
+          <t>48371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62748</t>
+          <t>62173</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95428</t>
+          <t>95216</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>316737</t>
+          <t>314876</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>340927</t>
+          <t>341928</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>305706</t>
+          <t>305120</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>332906</t>
+          <t>331289</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>630146</t>
+          <t>630388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>668030</t>
+          <t>666515</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34322</t>
+          <t>33321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58512</t>
+          <t>60373</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38255</t>
+          <t>39872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65455</t>
+          <t>66041</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78381</t>
+          <t>79896</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116265</t>
+          <t>116023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>426117</t>
+          <t>422633</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>458001</t>
+          <t>456940</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>133467</t>
+          <t>133662</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151588</t>
+          <t>152177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>565822</t>
+          <t>564883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>604527</t>
+          <t>602916</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,47%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57346</t>
+          <t>58407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89230</t>
+          <t>92714</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32656</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76943</t>
+          <t>78554</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115648</t>
+          <t>116587</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>948976</t>
+          <t>945615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>999131</t>
+          <t>997252</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>664518</t>
+          <t>665923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>708923</t>
+          <t>707827</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1626153</t>
+          <t>1627262</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1691739</t>
+          <t>1692343</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146611</t>
+          <t>148490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196766</t>
+          <t>200127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114808</t>
+          <t>115904</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159213</t>
+          <t>157808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>277734</t>
+          <t>277130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>343320</t>
+          <t>342211</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>499260</t>
+          <t>497757</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>537383</t>
+          <t>535327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>619891</t>
+          <t>621754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>655667</t>
+          <t>657802</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1130172</t>
+          <t>1129110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1181340</t>
+          <t>1181368</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78808</t>
+          <t>80864</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116931</t>
+          <t>118434</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79189</t>
+          <t>77054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>114965</t>
+          <t>113102</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>169707</t>
+          <t>169679</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>220875</t>
+          <t>221937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>170981</t>
+          <t>171865</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>204012</t>
+          <t>205358</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>919661</t>
+          <t>919518</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>961372</t>
+          <t>962334</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1104365</t>
+          <t>1102918</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1159147</t>
+          <t>1158288</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80980</t>
+          <t>79634</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114011</t>
+          <t>113127</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>106268</t>
+          <t>105306</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>147979</t>
+          <t>148122</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>193484</t>
+          <t>194343</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>248266</t>
+          <t>249713</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2793139</t>
+          <t>2789882</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2877400</t>
+          <t>2877959</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3001065</t>
+          <t>2996685</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3080602</t>
+          <t>3079887</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5824636</t>
+          <t>5820729</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5940332</t>
+          <t>5940220</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>485077</t>
+          <t>484518</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>569338</t>
+          <t>572595</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>428719</t>
+          <t>429434</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>508256</t>
+          <t>512636</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>931467</t>
+          <t>931579</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1047163</t>
+          <t>1051070</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -3361,32 +3361,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>403088</t>
+          <t>435141</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>382858</t>
+          <t>415589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>419255</t>
+          <t>453618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3396,32 +3396,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>378190</t>
+          <t>408380</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>365084</t>
+          <t>392709</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>390686</t>
+          <t>422326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3431,32 +3431,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>781277</t>
+          <t>843520</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>757536</t>
+          <t>815849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>800685</t>
+          <t>866359</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -3474,32 +3474,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>102124</t>
+          <t>115477</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85957</t>
+          <t>97000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>122354</t>
+          <t>135029</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3509,32 +3509,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67188</t>
+          <t>77954</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54692</t>
+          <t>64008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80294</t>
+          <t>93625</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3544,32 +3544,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>169313</t>
+          <t>193432</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149905</t>
+          <t>170593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>193054</t>
+          <t>221103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3622,17 +3622,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>445378</t>
+          <t>486334</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>445378</t>
+          <t>486334</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>445378</t>
+          <t>486334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>950590</t>
+          <t>1036952</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>950590</t>
+          <t>1036952</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>950590</t>
+          <t>1036952</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>338218</t>
+          <t>359113</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>318803</t>
+          <t>339359</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>356233</t>
+          <t>377795</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>303363</t>
+          <t>333315</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>288262</t>
+          <t>315847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>316764</t>
+          <t>346955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3774,32 +3774,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>641580</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>615763</t>
+          <t>665457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>663584</t>
+          <t>719075</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -3817,32 +3817,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>113995</t>
+          <t>124099</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95980</t>
+          <t>105417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133410</t>
+          <t>143853</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3852,32 +3852,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>79217</t>
+          <t>89828</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65816</t>
+          <t>76188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94318</t>
+          <t>107296</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3887,32 +3887,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>193213</t>
+          <t>213928</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171209</t>
+          <t>187280</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>219030</t>
+          <t>240898</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4047,32 +4047,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>543151</t>
+          <t>331154</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>459495</t>
+          <t>310704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>620370</t>
+          <t>351471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4082,32 +4082,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>129903</t>
+          <t>145166</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>121836</t>
+          <t>134230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138277</t>
+          <t>153511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4117,32 +4117,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>673053</t>
+          <t>476320</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>599778</t>
+          <t>454133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>765560</t>
+          <t>500248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -4160,32 +4160,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>124276</t>
+          <t>139593</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47057</t>
+          <t>119276</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>207932</t>
+          <t>160043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4195,32 +4195,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37008</t>
+          <t>42331</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28634</t>
+          <t>33986</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45075</t>
+          <t>53267</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4230,32 +4230,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>161284</t>
+          <t>181924</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68777</t>
+          <t>157996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234559</t>
+          <t>204111</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4308,17 +4308,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834337</t>
+          <t>658244</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834337</t>
+          <t>658244</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834337</t>
+          <t>658244</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4390,32 +4390,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>725683</t>
+          <t>798637</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>692259</t>
+          <t>765324</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>765254</t>
+          <t>833317</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4425,32 +4425,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>793548</t>
+          <t>649915</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>734778</t>
+          <t>626133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>889078</t>
+          <t>672696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4460,32 +4460,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1519231</t>
+          <t>1448552</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1443175</t>
+          <t>1407295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1668235</t>
+          <t>1486057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>74,68%</t>
         </is>
       </c>
     </row>
@@ -4503,32 +4503,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>308217</t>
+          <t>332133</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>268646</t>
+          <t>297453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>341641</t>
+          <t>365446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4538,32 +4538,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>183161</t>
+          <t>209300</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87631</t>
+          <t>186519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>241931</t>
+          <t>233082</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4573,32 +4573,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>491378</t>
+          <t>541433</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>342374</t>
+          <t>503928</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>567434</t>
+          <t>582690</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033900</t>
+          <t>1130770</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033900</t>
+          <t>1130770</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033900</t>
+          <t>1130770</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>976709</t>
+          <t>859215</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>976709</t>
+          <t>859215</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>976709</t>
+          <t>859215</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010609</t>
+          <t>1989985</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010609</t>
+          <t>1989985</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010609</t>
+          <t>1989985</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4733,32 +4733,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>309909</t>
+          <t>372266</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>285535</t>
+          <t>348063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>332506</t>
+          <t>395755</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4768,32 +4768,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>659484</t>
+          <t>622533</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>628500</t>
+          <t>601130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>708339</t>
+          <t>643891</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4803,32 +4803,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>969394</t>
+          <t>994799</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>926137</t>
+          <t>962427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1031910</t>
+          <t>1027085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>73,57%</t>
         </is>
       </c>
     </row>
@@ -4846,32 +4846,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>163147</t>
+          <t>193679</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140550</t>
+          <t>170190</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187521</t>
+          <t>217882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4881,32 +4881,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>181689</t>
+          <t>207573</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132834</t>
+          <t>186215</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212673</t>
+          <t>228976</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4916,32 +4916,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>344836</t>
+          <t>401252</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282320</t>
+          <t>368966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388093</t>
+          <t>433624</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -4959,17 +4959,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473056</t>
+          <t>565945</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473056</t>
+          <t>565945</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473056</t>
+          <t>565945</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841173</t>
+          <t>830106</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841173</t>
+          <t>830106</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841173</t>
+          <t>830106</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5029,17 +5029,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314230</t>
+          <t>1396051</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314230</t>
+          <t>1396051</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314230</t>
+          <t>1396051</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5076,32 +5076,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>170262</t>
+          <t>157778</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>146124</t>
+          <t>134846</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>192750</t>
+          <t>178129</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5111,32 +5111,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>556600</t>
+          <t>609387</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>531398</t>
+          <t>583595</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>580378</t>
+          <t>634659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5146,32 +5146,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>726862</t>
+          <t>767165</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>693692</t>
+          <t>728939</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>758091</t>
+          <t>798439</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -5189,32 +5189,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>69149</t>
+          <t>78251</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46661</t>
+          <t>57900</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93287</t>
+          <t>101183</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5224,32 +5224,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>204223</t>
+          <t>234283</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>180445</t>
+          <t>209011</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>229425</t>
+          <t>260075</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5259,32 +5259,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>273372</t>
+          <t>312534</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>242143</t>
+          <t>281260</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>306542</t>
+          <t>350760</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5302,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>239411</t>
+          <t>236029</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239411</t>
+          <t>236029</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>239411</t>
+          <t>236029</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760823</t>
+          <t>843670</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760823</t>
+          <t>843670</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760823</t>
+          <t>843670</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5372,17 +5372,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000234</t>
+          <t>1079699</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000234</t>
+          <t>1079699</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000234</t>
+          <t>1079699</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2490311</t>
+          <t>2454087</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2400659</t>
+          <t>2398262</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2721840</t>
+          <t>2512188</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5454,32 +5454,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2821088</t>
+          <t>2768697</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2750875</t>
+          <t>2723676</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2957921</t>
+          <t>2815983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5489,32 +5489,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5311398</t>
+          <t>5222784</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5185839</t>
+          <t>5149587</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5551346</t>
+          <t>5296804</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -5532,32 +5532,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>880908</t>
+          <t>983234</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649379</t>
+          <t>925133</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>970560</t>
+          <t>1039059</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5567,32 +5567,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>752487</t>
+          <t>861268</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>615654</t>
+          <t>813982</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>822700</t>
+          <t>906289</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5602,32 +5602,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1633395</t>
+          <t>1844502</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1393447</t>
+          <t>1770482</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1758954</t>
+          <t>1917699</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -5645,17 +5645,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3371219</t>
+          <t>3437321</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3371219</t>
+          <t>3437321</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3371219</t>
+          <t>3437321</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573575</t>
+          <t>3629965</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573575</t>
+          <t>3629965</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573575</t>
+          <t>3629965</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5715,17 +5715,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6944793</t>
+          <t>7067286</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6944793</t>
+          <t>7067286</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6944793</t>
+          <t>7067286</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
